--- a/data/B24_department_schedules_midterms/Çevre Mühendisliği.xlsx
+++ b/data/B24_department_schedules_midterms/Çevre Mühendisliği.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_midterms/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/B24_department_schedules_midterms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{73EA8EB4-B532-4208-98EB-A12DAEDB9EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31FF252D-4158-414C-86CD-3F74195D6827}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{73EA8EB4-B532-4208-98EB-A12DAEDB9EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFE0901A-DEE7-462F-80A9-9EACDEF90002}"/>
   <bookViews>
-    <workbookView xWindow="-8910" yWindow="-13500" windowWidth="22080" windowHeight="9315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
   <si>
     <t>Year:</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>Amfi 3</t>
+  </si>
+  <si>
+    <t>timeslots</t>
   </si>
 </sst>
 </file>
@@ -305,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -329,11 +332,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -395,15 +405,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6CCEB3C6-E865-4295-8FE4-F476D4D417BB}" name="Table1" displayName="Table1" ref="A1:F27" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:F27" xr:uid="{6CCEB3C6-E865-4295-8FE4-F476D4D417BB}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{C4437867-2534-4236-B6AB-5C3E485ACB49}" name="Year:" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{EADDAB49-7C50-4B3C-BFF5-E79F2400D882}" name="Course ID" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{F699FC73-49EC-4E47-879F-593C800FD533}" name="Date" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{77A316F6-1D1E-4587-A285-E742C9DD1DB5}" name="Rooms" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{6B7416AA-CF55-42CC-B83E-CB1D385E192C}" name="Course Name" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6CCEB3C6-E865-4295-8FE4-F476D4D417BB}" name="Table1" displayName="Table1" ref="A1:G27" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:G27" xr:uid="{6CCEB3C6-E865-4295-8FE4-F476D4D417BB}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{C4437867-2534-4236-B6AB-5C3E485ACB49}" name="Year:" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{EADDAB49-7C50-4B3C-BFF5-E79F2400D882}" name="Course ID" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{F699FC73-49EC-4E47-879F-593C800FD533}" name="Date" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{77A316F6-1D1E-4587-A285-E742C9DD1DB5}" name="Rooms" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{6B7416AA-CF55-42CC-B83E-CB1D385E192C}" name="Course Name" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{12B093FB-CE67-437D-A74D-B80C5470270A}" name="Rooms Used"/>
+    <tableColumn id="7" xr3:uid="{B54247EC-1288-41B0-93BF-4A6EB5B227B6}" name="timeslots" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -696,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="10.9296875" customWidth="1"/>
@@ -704,7 +715,7 @@
     <col min="6" max="6" width="46.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,8 +734,11 @@
       <c r="F1" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -743,8 +757,12 @@
       <c r="F2" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G2" s="11">
+        <v>2</v>
+      </c>
+      <c r="J2" s="12"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -763,8 +781,12 @@
       <c r="F3" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G3" s="11">
+        <v>2</v>
+      </c>
+      <c r="J3" s="12"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -783,8 +805,12 @@
       <c r="F4" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G4" s="11">
+        <v>2</v>
+      </c>
+      <c r="J4" s="12"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -803,8 +829,12 @@
       <c r="F5" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G5" s="11">
+        <v>9</v>
+      </c>
+      <c r="J5" s="12"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -823,8 +853,11 @@
       <c r="F6" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G6" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -843,8 +876,12 @@
       <c r="F7" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G7" s="11">
+        <v>2</v>
+      </c>
+      <c r="J7" s="12"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -863,8 +900,12 @@
       <c r="F8" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G8" s="11">
+        <v>5</v>
+      </c>
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>1</v>
       </c>
@@ -883,8 +924,12 @@
       <c r="F9" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G9" s="11">
+        <v>5</v>
+      </c>
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="5">
         <v>2</v>
       </c>
@@ -903,8 +948,12 @@
       <c r="F10" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G10" s="11">
+        <v>5</v>
+      </c>
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="5">
         <v>2</v>
       </c>
@@ -923,8 +972,11 @@
       <c r="F11" s="6" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G11" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="5">
         <v>2</v>
       </c>
@@ -943,8 +995,11 @@
       <c r="F12" s="6" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G12" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="5">
         <v>2</v>
       </c>
@@ -963,8 +1018,11 @@
       <c r="F13" s="6" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G13" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="5">
         <v>2</v>
       </c>
@@ -983,8 +1041,11 @@
       <c r="F14" s="6" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G14" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="5">
         <v>2</v>
       </c>
@@ -1003,8 +1064,11 @@
       <c r="F15" s="6" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G15" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="5">
         <v>2</v>
       </c>
@@ -1023,8 +1087,11 @@
       <c r="F16" s="6" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G16" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="7">
         <v>3</v>
       </c>
@@ -1043,8 +1110,11 @@
       <c r="F17" s="8" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G17" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="7">
         <v>3</v>
       </c>
@@ -1063,8 +1133,11 @@
       <c r="F18" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G18" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="7">
         <v>3</v>
       </c>
@@ -1083,8 +1156,11 @@
       <c r="F19" s="8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G19" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="7">
         <v>3</v>
       </c>
@@ -1103,8 +1179,11 @@
       <c r="F20" s="8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G20" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="7">
         <v>3</v>
       </c>
@@ -1123,8 +1202,11 @@
       <c r="F21" s="8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G21" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="7">
         <v>3</v>
       </c>
@@ -1143,8 +1225,11 @@
       <c r="F22" s="8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G22" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="9">
         <v>4</v>
       </c>
@@ -1163,8 +1248,11 @@
       <c r="F23" s="10" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G23" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="9">
         <v>4</v>
       </c>
@@ -1183,8 +1271,11 @@
       <c r="F24" s="10" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G24" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="9">
         <v>4</v>
       </c>
@@ -1203,8 +1294,11 @@
       <c r="F25" s="10" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G25" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="9">
         <v>4</v>
       </c>
@@ -1223,8 +1317,11 @@
       <c r="F26" s="10" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G26" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="9">
         <v>4</v>
       </c>
@@ -1242,6 +1339,9 @@
       </c>
       <c r="F27" s="10" t="s">
         <v>61</v>
+      </c>
+      <c r="G27" s="11">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
